--- a/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_06.xlsx
+++ b/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_06.xlsx
@@ -670,7 +670,7 @@
     <t>Krstovic</t>
   </si>
   <si>
-    <t>D'aversa</t>
+    <t>D'Aversa</t>
   </si>
   <si>
     <t>Milan</t>
@@ -817,7 +817,7 @@
     <t>Lindstrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Cajuste </t>
+    <t>Cajuste</t>
   </si>
   <si>
     <t>Simeone</t>
@@ -847,7 +847,7 @@
     <t>Mancini</t>
   </si>
   <si>
-    <t>N'dicka</t>
+    <t>N'Dicka</t>
   </si>
   <si>
     <t>Llorente D.</t>
@@ -1276,7 +1276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:O382"/>
+  <dimension ref="A1:M382"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1419,8 +1419,6 @@
       <c r="M6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
     </row>
     <row r="7">
       <c r="A7" s="0">
@@ -1535,8 +1533,8 @@
       <c r="J9" s="10">
         <v>0</v>
       </c>
-      <c r="K9" s="1">
-        <v>1</v>
+      <c r="K9" s="10">
+        <v>0</v>
       </c>
       <c r="L9" s="10">
         <v>0</v>
@@ -2176,8 +2174,6 @@
       <c r="M25" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
     </row>
     <row r="26">
       <c r="A26" s="11">
@@ -2933,8 +2929,6 @@
       <c r="M44" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
     </row>
     <row r="45">
       <c r="A45" s="0">
@@ -3690,8 +3684,6 @@
       <c r="M63" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N63" s="8"/>
-      <c r="O63" s="8"/>
     </row>
     <row r="64">
       <c r="A64" s="11">
@@ -4447,8 +4439,6 @@
       <c r="M82" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N82" s="8"/>
-      <c r="O82" s="8"/>
     </row>
     <row r="83">
       <c r="A83" s="0">
@@ -5204,8 +5194,6 @@
       <c r="M101" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N101" s="8"/>
-      <c r="O101" s="8"/>
     </row>
     <row r="102">
       <c r="A102" s="11">
@@ -5961,8 +5949,6 @@
       <c r="M120" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N120" s="8"/>
-      <c r="O120" s="8"/>
     </row>
     <row r="121">
       <c r="A121" s="0">
@@ -6677,8 +6663,6 @@
       <c r="M138" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N138" s="8"/>
-      <c r="O138" s="8"/>
     </row>
     <row r="139">
       <c r="A139" s="0">
@@ -7434,8 +7418,6 @@
       <c r="M157" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N157" s="8"/>
-      <c r="O157" s="8"/>
     </row>
     <row r="158">
       <c r="A158" s="11">
@@ -8191,8 +8173,6 @@
       <c r="M176" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N176" s="8"/>
-      <c r="O176" s="8"/>
     </row>
     <row r="177">
       <c r="A177" s="0">
@@ -8907,8 +8887,6 @@
       <c r="M194" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N194" s="8"/>
-      <c r="O194" s="8"/>
     </row>
     <row r="195">
       <c r="A195" s="0">
@@ -9664,8 +9642,6 @@
       <c r="M213" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N213" s="8"/>
-      <c r="O213" s="8"/>
     </row>
     <row r="214">
       <c r="A214" s="11">
@@ -10421,8 +10397,6 @@
       <c r="M232" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N232" s="8"/>
-      <c r="O232" s="8"/>
     </row>
     <row r="233">
       <c r="A233" s="0">
@@ -11178,8 +11152,6 @@
       <c r="M251" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N251" s="8"/>
-      <c r="O251" s="8"/>
     </row>
     <row r="252">
       <c r="A252" s="11">
@@ -11935,8 +11907,6 @@
       <c r="M270" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N270" s="8"/>
-      <c r="O270" s="8"/>
     </row>
     <row r="271">
       <c r="A271" s="0">
@@ -12692,8 +12662,6 @@
       <c r="M289" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N289" s="8"/>
-      <c r="O289" s="8"/>
     </row>
     <row r="290">
       <c r="A290" s="11">
@@ -13449,8 +13417,6 @@
       <c r="M308" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N308" s="8"/>
-      <c r="O308" s="8"/>
     </row>
     <row r="309">
       <c r="A309" s="0">
@@ -14206,8 +14172,6 @@
       <c r="M327" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N327" s="8"/>
-      <c r="O327" s="8"/>
     </row>
     <row r="328">
       <c r="A328" s="11">
@@ -14963,8 +14927,6 @@
       <c r="M346" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N346" s="8"/>
-      <c r="O346" s="8"/>
     </row>
     <row r="347">
       <c r="A347" s="0">
@@ -15720,8 +15682,6 @@
       <c r="M365" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N365" s="8"/>
-      <c r="O365" s="8"/>
     </row>
     <row r="366">
       <c r="A366" s="11">
@@ -16453,7 +16413,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:O382"/>
+  <dimension ref="A1:M382"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -16596,8 +16556,6 @@
       <c r="M6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
     </row>
     <row r="7">
       <c r="A7" s="0">
@@ -16712,8 +16670,8 @@
       <c r="J9" s="10">
         <v>0</v>
       </c>
-      <c r="K9" s="1">
-        <v>1</v>
+      <c r="K9" s="10">
+        <v>0</v>
       </c>
       <c r="L9" s="10">
         <v>0</v>
@@ -17353,8 +17311,6 @@
       <c r="M25" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
     </row>
     <row r="26">
       <c r="A26" s="11">
@@ -18110,8 +18066,6 @@
       <c r="M44" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
     </row>
     <row r="45">
       <c r="A45" s="0">
@@ -18867,8 +18821,6 @@
       <c r="M63" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N63" s="8"/>
-      <c r="O63" s="8"/>
     </row>
     <row r="64">
       <c r="A64" s="11">
@@ -19624,8 +19576,6 @@
       <c r="M82" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N82" s="8"/>
-      <c r="O82" s="8"/>
     </row>
     <row r="83">
       <c r="A83" s="0">
@@ -20381,8 +20331,6 @@
       <c r="M101" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N101" s="8"/>
-      <c r="O101" s="8"/>
     </row>
     <row r="102">
       <c r="A102" s="11">
@@ -21138,8 +21086,6 @@
       <c r="M120" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N120" s="8"/>
-      <c r="O120" s="8"/>
     </row>
     <row r="121">
       <c r="A121" s="0">
@@ -21854,8 +21800,6 @@
       <c r="M138" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N138" s="8"/>
-      <c r="O138" s="8"/>
     </row>
     <row r="139">
       <c r="A139" s="0">
@@ -22611,8 +22555,6 @@
       <c r="M157" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N157" s="8"/>
-      <c r="O157" s="8"/>
     </row>
     <row r="158">
       <c r="A158" s="11">
@@ -23368,8 +23310,6 @@
       <c r="M176" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N176" s="8"/>
-      <c r="O176" s="8"/>
     </row>
     <row r="177">
       <c r="A177" s="0">
@@ -24084,8 +24024,6 @@
       <c r="M194" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N194" s="8"/>
-      <c r="O194" s="8"/>
     </row>
     <row r="195">
       <c r="A195" s="0">
@@ -24841,8 +24779,6 @@
       <c r="M213" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N213" s="8"/>
-      <c r="O213" s="8"/>
     </row>
     <row r="214">
       <c r="A214" s="11">
@@ -25598,8 +25534,6 @@
       <c r="M232" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N232" s="8"/>
-      <c r="O232" s="8"/>
     </row>
     <row r="233">
       <c r="A233" s="0">
@@ -26355,8 +26289,6 @@
       <c r="M251" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N251" s="8"/>
-      <c r="O251" s="8"/>
     </row>
     <row r="252">
       <c r="A252" s="11">
@@ -27112,8 +27044,6 @@
       <c r="M270" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N270" s="8"/>
-      <c r="O270" s="8"/>
     </row>
     <row r="271">
       <c r="A271" s="0">
@@ -27869,8 +27799,6 @@
       <c r="M289" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N289" s="8"/>
-      <c r="O289" s="8"/>
     </row>
     <row r="290">
       <c r="A290" s="11">
@@ -28626,8 +28554,6 @@
       <c r="M308" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N308" s="8"/>
-      <c r="O308" s="8"/>
     </row>
     <row r="309">
       <c r="A309" s="0">
@@ -29383,8 +29309,6 @@
       <c r="M327" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N327" s="8"/>
-      <c r="O327" s="8"/>
     </row>
     <row r="328">
       <c r="A328" s="11">
@@ -30140,8 +30064,6 @@
       <c r="M346" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N346" s="8"/>
-      <c r="O346" s="8"/>
     </row>
     <row r="347">
       <c r="A347" s="0">
@@ -30897,8 +30819,6 @@
       <c r="M365" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N365" s="8"/>
-      <c r="O365" s="8"/>
     </row>
     <row r="366">
       <c r="A366" s="11">
@@ -31630,7 +31550,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:O382"/>
+  <dimension ref="A1:M382"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -31773,8 +31693,6 @@
       <c r="M6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
     </row>
     <row r="7">
       <c r="A7" s="0">
@@ -31889,8 +31807,8 @@
       <c r="J9" s="10">
         <v>0</v>
       </c>
-      <c r="K9" s="1">
-        <v>1</v>
+      <c r="K9" s="10">
+        <v>0</v>
       </c>
       <c r="L9" s="10">
         <v>0</v>
@@ -32530,8 +32448,6 @@
       <c r="M25" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
     </row>
     <row r="26">
       <c r="A26" s="11">
@@ -33287,8 +33203,6 @@
       <c r="M44" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
     </row>
     <row r="45">
       <c r="A45" s="0">
@@ -34044,8 +33958,6 @@
       <c r="M63" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N63" s="8"/>
-      <c r="O63" s="8"/>
     </row>
     <row r="64">
       <c r="A64" s="11">
@@ -34801,8 +34713,6 @@
       <c r="M82" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N82" s="8"/>
-      <c r="O82" s="8"/>
     </row>
     <row r="83">
       <c r="A83" s="0">
@@ -35558,8 +35468,6 @@
       <c r="M101" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N101" s="8"/>
-      <c r="O101" s="8"/>
     </row>
     <row r="102">
       <c r="A102" s="11">
@@ -36315,8 +36223,6 @@
       <c r="M120" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N120" s="8"/>
-      <c r="O120" s="8"/>
     </row>
     <row r="121">
       <c r="A121" s="0">
@@ -37031,8 +36937,6 @@
       <c r="M138" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N138" s="8"/>
-      <c r="O138" s="8"/>
     </row>
     <row r="139">
       <c r="A139" s="0">
@@ -37788,8 +37692,6 @@
       <c r="M157" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N157" s="8"/>
-      <c r="O157" s="8"/>
     </row>
     <row r="158">
       <c r="A158" s="11">
@@ -38545,8 +38447,6 @@
       <c r="M176" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N176" s="8"/>
-      <c r="O176" s="8"/>
     </row>
     <row r="177">
       <c r="A177" s="0">
@@ -39261,8 +39161,6 @@
       <c r="M194" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N194" s="8"/>
-      <c r="O194" s="8"/>
     </row>
     <row r="195">
       <c r="A195" s="0">
@@ -40018,8 +39916,6 @@
       <c r="M213" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N213" s="8"/>
-      <c r="O213" s="8"/>
     </row>
     <row r="214">
       <c r="A214" s="11">
@@ -40775,8 +40671,6 @@
       <c r="M232" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N232" s="8"/>
-      <c r="O232" s="8"/>
     </row>
     <row r="233">
       <c r="A233" s="0">
@@ -41532,8 +41426,6 @@
       <c r="M251" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N251" s="8"/>
-      <c r="O251" s="8"/>
     </row>
     <row r="252">
       <c r="A252" s="11">
@@ -42289,8 +42181,6 @@
       <c r="M270" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N270" s="8"/>
-      <c r="O270" s="8"/>
     </row>
     <row r="271">
       <c r="A271" s="0">
@@ -43046,8 +42936,6 @@
       <c r="M289" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N289" s="8"/>
-      <c r="O289" s="8"/>
     </row>
     <row r="290">
       <c r="A290" s="11">
@@ -43803,8 +43691,6 @@
       <c r="M308" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N308" s="8"/>
-      <c r="O308" s="8"/>
     </row>
     <row r="309">
       <c r="A309" s="0">
@@ -44560,8 +44446,6 @@
       <c r="M327" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N327" s="8"/>
-      <c r="O327" s="8"/>
     </row>
     <row r="328">
       <c r="A328" s="11">
@@ -45317,8 +45201,6 @@
       <c r="M346" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N346" s="8"/>
-      <c r="O346" s="8"/>
     </row>
     <row r="347">
       <c r="A347" s="0">
@@ -46074,8 +45956,6 @@
       <c r="M365" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N365" s="8"/>
-      <c r="O365" s="8"/>
     </row>
     <row r="366">
       <c r="A366" s="11">

--- a/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_06.xlsx
+++ b/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_06.xlsx
@@ -670,7 +670,7 @@
     <t>Krstovic</t>
   </si>
   <si>
-    <t>D'aversa</t>
+    <t>D'Aversa</t>
   </si>
   <si>
     <t>Milan</t>
@@ -817,7 +817,7 @@
     <t>Lindstrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Cajuste </t>
+    <t>Cajuste</t>
   </si>
   <si>
     <t>Simeone</t>
@@ -847,7 +847,7 @@
     <t>Mancini</t>
   </si>
   <si>
-    <t>N'dicka</t>
+    <t>N'Dicka</t>
   </si>
   <si>
     <t>Llorente D.</t>
@@ -1276,7 +1276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:O382"/>
+  <dimension ref="A1:M382"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1419,8 +1419,6 @@
       <c r="M6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
     </row>
     <row r="7">
       <c r="A7" s="0">
@@ -2176,8 +2174,6 @@
       <c r="M25" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
     </row>
     <row r="26">
       <c r="A26" s="11">
@@ -2933,8 +2929,6 @@
       <c r="M44" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
     </row>
     <row r="45">
       <c r="A45" s="0">
@@ -3690,8 +3684,6 @@
       <c r="M63" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N63" s="8"/>
-      <c r="O63" s="8"/>
     </row>
     <row r="64">
       <c r="A64" s="11">
@@ -4447,8 +4439,6 @@
       <c r="M82" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N82" s="8"/>
-      <c r="O82" s="8"/>
     </row>
     <row r="83">
       <c r="A83" s="0">
@@ -5204,8 +5194,6 @@
       <c r="M101" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N101" s="8"/>
-      <c r="O101" s="8"/>
     </row>
     <row r="102">
       <c r="A102" s="11">
@@ -5961,8 +5949,6 @@
       <c r="M120" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N120" s="8"/>
-      <c r="O120" s="8"/>
     </row>
     <row r="121">
       <c r="A121" s="0">
@@ -6677,8 +6663,6 @@
       <c r="M138" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N138" s="8"/>
-      <c r="O138" s="8"/>
     </row>
     <row r="139">
       <c r="A139" s="0">
@@ -7434,8 +7418,6 @@
       <c r="M157" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N157" s="8"/>
-      <c r="O157" s="8"/>
     </row>
     <row r="158">
       <c r="A158" s="11">
@@ -8191,8 +8173,6 @@
       <c r="M176" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N176" s="8"/>
-      <c r="O176" s="8"/>
     </row>
     <row r="177">
       <c r="A177" s="0">
@@ -8907,8 +8887,6 @@
       <c r="M194" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N194" s="8"/>
-      <c r="O194" s="8"/>
     </row>
     <row r="195">
       <c r="A195" s="0">
@@ -9664,8 +9642,6 @@
       <c r="M213" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N213" s="8"/>
-      <c r="O213" s="8"/>
     </row>
     <row r="214">
       <c r="A214" s="11">
@@ -10421,8 +10397,6 @@
       <c r="M232" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N232" s="8"/>
-      <c r="O232" s="8"/>
     </row>
     <row r="233">
       <c r="A233" s="0">
@@ -11178,8 +11152,6 @@
       <c r="M251" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N251" s="8"/>
-      <c r="O251" s="8"/>
     </row>
     <row r="252">
       <c r="A252" s="11">
@@ -11935,8 +11907,6 @@
       <c r="M270" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N270" s="8"/>
-      <c r="O270" s="8"/>
     </row>
     <row r="271">
       <c r="A271" s="0">
@@ -12692,8 +12662,6 @@
       <c r="M289" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N289" s="8"/>
-      <c r="O289" s="8"/>
     </row>
     <row r="290">
       <c r="A290" s="11">
@@ -13449,8 +13417,6 @@
       <c r="M308" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N308" s="8"/>
-      <c r="O308" s="8"/>
     </row>
     <row r="309">
       <c r="A309" s="0">
@@ -14206,8 +14172,6 @@
       <c r="M327" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N327" s="8"/>
-      <c r="O327" s="8"/>
     </row>
     <row r="328">
       <c r="A328" s="11">
@@ -14963,8 +14927,6 @@
       <c r="M346" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N346" s="8"/>
-      <c r="O346" s="8"/>
     </row>
     <row r="347">
       <c r="A347" s="0">
@@ -15720,8 +15682,6 @@
       <c r="M365" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N365" s="8"/>
-      <c r="O365" s="8"/>
     </row>
     <row r="366">
       <c r="A366" s="11">
@@ -16453,7 +16413,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:O382"/>
+  <dimension ref="A1:M382"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -16596,8 +16556,6 @@
       <c r="M6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
     </row>
     <row r="7">
       <c r="A7" s="0">
@@ -17353,8 +17311,6 @@
       <c r="M25" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
     </row>
     <row r="26">
       <c r="A26" s="11">
@@ -18110,8 +18066,6 @@
       <c r="M44" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
     </row>
     <row r="45">
       <c r="A45" s="0">
@@ -18867,8 +18821,6 @@
       <c r="M63" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N63" s="8"/>
-      <c r="O63" s="8"/>
     </row>
     <row r="64">
       <c r="A64" s="11">
@@ -19624,8 +19576,6 @@
       <c r="M82" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N82" s="8"/>
-      <c r="O82" s="8"/>
     </row>
     <row r="83">
       <c r="A83" s="0">
@@ -20381,8 +20331,6 @@
       <c r="M101" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N101" s="8"/>
-      <c r="O101" s="8"/>
     </row>
     <row r="102">
       <c r="A102" s="11">
@@ -21138,8 +21086,6 @@
       <c r="M120" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N120" s="8"/>
-      <c r="O120" s="8"/>
     </row>
     <row r="121">
       <c r="A121" s="0">
@@ -21854,8 +21800,6 @@
       <c r="M138" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N138" s="8"/>
-      <c r="O138" s="8"/>
     </row>
     <row r="139">
       <c r="A139" s="0">
@@ -22611,8 +22555,6 @@
       <c r="M157" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N157" s="8"/>
-      <c r="O157" s="8"/>
     </row>
     <row r="158">
       <c r="A158" s="11">
@@ -23368,8 +23310,6 @@
       <c r="M176" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N176" s="8"/>
-      <c r="O176" s="8"/>
     </row>
     <row r="177">
       <c r="A177" s="0">
@@ -24084,8 +24024,6 @@
       <c r="M194" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N194" s="8"/>
-      <c r="O194" s="8"/>
     </row>
     <row r="195">
       <c r="A195" s="0">
@@ -24841,8 +24779,6 @@
       <c r="M213" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N213" s="8"/>
-      <c r="O213" s="8"/>
     </row>
     <row r="214">
       <c r="A214" s="11">
@@ -25598,8 +25534,6 @@
       <c r="M232" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N232" s="8"/>
-      <c r="O232" s="8"/>
     </row>
     <row r="233">
       <c r="A233" s="0">
@@ -26355,8 +26289,6 @@
       <c r="M251" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N251" s="8"/>
-      <c r="O251" s="8"/>
     </row>
     <row r="252">
       <c r="A252" s="11">
@@ -27112,8 +27044,6 @@
       <c r="M270" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N270" s="8"/>
-      <c r="O270" s="8"/>
     </row>
     <row r="271">
       <c r="A271" s="0">
@@ -27869,8 +27799,6 @@
       <c r="M289" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N289" s="8"/>
-      <c r="O289" s="8"/>
     </row>
     <row r="290">
       <c r="A290" s="11">
@@ -28626,8 +28554,6 @@
       <c r="M308" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N308" s="8"/>
-      <c r="O308" s="8"/>
     </row>
     <row r="309">
       <c r="A309" s="0">
@@ -29383,8 +29309,6 @@
       <c r="M327" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N327" s="8"/>
-      <c r="O327" s="8"/>
     </row>
     <row r="328">
       <c r="A328" s="11">
@@ -30140,8 +30064,6 @@
       <c r="M346" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N346" s="8"/>
-      <c r="O346" s="8"/>
     </row>
     <row r="347">
       <c r="A347" s="0">
@@ -30897,8 +30819,6 @@
       <c r="M365" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N365" s="8"/>
-      <c r="O365" s="8"/>
     </row>
     <row r="366">
       <c r="A366" s="11">
@@ -31630,7 +31550,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:O382"/>
+  <dimension ref="A1:M382"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -31773,8 +31693,6 @@
       <c r="M6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
     </row>
     <row r="7">
       <c r="A7" s="0">
@@ -32530,8 +32448,6 @@
       <c r="M25" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
     </row>
     <row r="26">
       <c r="A26" s="11">
@@ -33287,8 +33203,6 @@
       <c r="M44" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
     </row>
     <row r="45">
       <c r="A45" s="0">
@@ -34044,8 +33958,6 @@
       <c r="M63" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N63" s="8"/>
-      <c r="O63" s="8"/>
     </row>
     <row r="64">
       <c r="A64" s="11">
@@ -34801,8 +34713,6 @@
       <c r="M82" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N82" s="8"/>
-      <c r="O82" s="8"/>
     </row>
     <row r="83">
       <c r="A83" s="0">
@@ -35558,8 +35468,6 @@
       <c r="M101" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N101" s="8"/>
-      <c r="O101" s="8"/>
     </row>
     <row r="102">
       <c r="A102" s="11">
@@ -36315,8 +36223,6 @@
       <c r="M120" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N120" s="8"/>
-      <c r="O120" s="8"/>
     </row>
     <row r="121">
       <c r="A121" s="0">
@@ -37031,8 +36937,6 @@
       <c r="M138" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N138" s="8"/>
-      <c r="O138" s="8"/>
     </row>
     <row r="139">
       <c r="A139" s="0">
@@ -37788,8 +37692,6 @@
       <c r="M157" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N157" s="8"/>
-      <c r="O157" s="8"/>
     </row>
     <row r="158">
       <c r="A158" s="11">
@@ -38545,8 +38447,6 @@
       <c r="M176" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N176" s="8"/>
-      <c r="O176" s="8"/>
     </row>
     <row r="177">
       <c r="A177" s="0">
@@ -39261,8 +39161,6 @@
       <c r="M194" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N194" s="8"/>
-      <c r="O194" s="8"/>
     </row>
     <row r="195">
       <c r="A195" s="0">
@@ -40018,8 +39916,6 @@
       <c r="M213" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N213" s="8"/>
-      <c r="O213" s="8"/>
     </row>
     <row r="214">
       <c r="A214" s="11">
@@ -40775,8 +40671,6 @@
       <c r="M232" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N232" s="8"/>
-      <c r="O232" s="8"/>
     </row>
     <row r="233">
       <c r="A233" s="0">
@@ -41532,8 +41426,6 @@
       <c r="M251" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N251" s="8"/>
-      <c r="O251" s="8"/>
     </row>
     <row r="252">
       <c r="A252" s="11">
@@ -42289,8 +42181,6 @@
       <c r="M270" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N270" s="8"/>
-      <c r="O270" s="8"/>
     </row>
     <row r="271">
       <c r="A271" s="0">
@@ -43046,8 +42936,6 @@
       <c r="M289" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N289" s="8"/>
-      <c r="O289" s="8"/>
     </row>
     <row r="290">
       <c r="A290" s="11">
@@ -43803,8 +43691,6 @@
       <c r="M308" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N308" s="8"/>
-      <c r="O308" s="8"/>
     </row>
     <row r="309">
       <c r="A309" s="0">
@@ -44560,8 +44446,6 @@
       <c r="M327" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N327" s="8"/>
-      <c r="O327" s="8"/>
     </row>
     <row r="328">
       <c r="A328" s="11">
@@ -45317,8 +45201,6 @@
       <c r="M346" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N346" s="8"/>
-      <c r="O346" s="8"/>
     </row>
     <row r="347">
       <c r="A347" s="0">
@@ -46074,8 +45956,6 @@
       <c r="M365" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N365" s="8"/>
-      <c r="O365" s="8"/>
     </row>
     <row r="366">
       <c r="A366" s="11">
